--- a/report/Draft Report 2.1_Project_Tracking_Template.xlsx
+++ b/report/Draft Report 2.1_Project_Tracking_Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="729">
   <si>
     <t>[Project Name] — Project Tracking Dashboard</t>
   </si>
@@ -1990,6 +1990,228 @@
   </si>
   <si>
     <t xml:space="preserve">BR-06: ignored AGV still a routing obstacle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet of 20 vehicles deadlocked. The planner validates a plan assuming every vehicle steps at the same time; in execution each vehicle moves at its own pace. A plan in which four vehicles each advance into the cell the next one is leaving passes that lockstep check, but at run time every vehicle waits for the one ahead to physically clear its cell. With no empty cell anywhere in the ring, none can move first and all four wait forever.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roughly one run in six froze the entire fleet; no scenario above 20 vehicles could be demonstrated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added cycle detection over the action-dependency graph (hasAdgCycle) and gated plan acceptance on it (isExecutableAsync), applied both to the incumbent plan and to the return path. Enabled by default via fms.mapf.adgAcyclic. The 20-vehicle scenario then passed 6 of 6 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The bounded node budget from I-002 was part of this fix, not a separate optimisation - without it the deadlock could not be reproduced reliably enough to diagnose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same planning problem produced four different plans across eight runs. The solver keeps improving its plan until a wall-clock deadline and returns the best found so far, so machine load decides how many iterations fit and therefore which plan comes back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression results could not be trusted: a red test often passed on rerun, so no solver change could be judged by a before/after run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaced the wall-clock cut-off with a fixed search-node budget of 200,000 nodes, making the solver deterministic for a given input. The 20-vehicle deadlock then reproduced on every run and could be traced to its root cause.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suite runtime also dropped from 1m21s to 18s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicles collided beyond the planning window. The planner only checks vehicles against each other inside a limited look-ahead window; past that window it appended each vehicle's remaining route to its goal with no mutual collision check at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every tail measured collided - 448 of 448 - and a fleet of 25 vehicles could not complete a run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three changes were required together: a fallback gate on the executable flag, restricting certification to the planning window (certifyWindowOnly), and parking idle vehicles off the running lanes. The full suite then passed 5 of 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">certifyWindowOnly on its own made matters worse - 20 vehicles failed 3 of 3 runs until the fallback gate was also in place. A patch must not be judged while the change it depends on is missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A frozen fleet never recovered on its own. Dispatching was triggered only by events such as an order arriving or a vehicle finishing a move. Once the whole fleet was stuck no event could fire, so dispatch was never called and nothing re-planned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A live log showed zero dispatch() calls across ten minutes; any deadlock was permanent rather than transient and needed a manual restart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added a one-second timer in FMSDispatcher that calls dispatch() whenever the planner is overdue, so recovery no longer depends on an event that will never arrive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The timer task must catch Throwable - scheduleAtFixedRate stops forever, silently, if the task throws.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map uploads made through WES silently lost vehicle properties. The XML parser did not read &lt;property&gt; children of &lt;vehicle&gt;, so preferredAdapterClass and every vda5050 setting was dropped before the model reached the kernel. The kernel then attached the default loopback driver instead of the VDA5050 driver, with no error reported anywhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The VDA5050 integration could never work through the WES upload path. Two days were spent looking for the fault in the MQTT layer and the vehicle simulator before the loss was traced to the upload path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added property to the parser's array tags and a properties field to the vehicle DTO. Verified end to end: uploading the VDA5050 map through WES now delivers all 9 properties to the kernel. 292 tests pass.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remains open because properties of point, path and location elements are still dropped by the same parser - same defect class, not yet fixed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicles oscillated back and forth instead of making progress. The anti-starvation mechanism raised a vehicle's priority only while it appeared stuck, and stuck was measured against the distance travelled since the previous step. A vehicle moving back and forth therefore kept resetting its own counter and never earned the boost, while a vehicle standing completely still did - so oscillating was rewarded over waiting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longer completion times across the fleet and repeated resource-claim churn, worsening as fleet size grew.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured progress against the best distance achieved so far and against the current leg goal, rather than against the previous step. Measured result: 10 vehicles -15% ticks, 25 vehicles -40% ticks, claim churn -48% and -63%, solver failures 14 down to 8, suite 128 of 128 green.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flips counter did not detect this fix (-2%) and must not be used as a health metric - it counts changes, not reversals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicles stopped responding and had to be reset. When the resource claim held by the scheduler drifted out of step with the allocation actually being requested, the kernel rejected the request with an exception that killed the vehicle's command pump, leaving the vehicle alive but unable to accept any further movement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual vehicles dropped out of service during a run until restarted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The scheduler now re-syncs the claim before allocating: it locates the requested allocation on the claimed route and drops the stale prefix, so the rejected condition no longer arises. No exception handler was added - the cause was removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual: when the requested allocation is not on the claimed route at all, the repair re-claims it alone and look-ahead is lost until the next drive order update. Logged as a warning and self-recovering, but it degrades routing quality - watch it as fleet size grows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deleting an operational location does not check for cargo still referencing it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create cargo whose destination is zone Z. 2. Before delivery, delete zone Z.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deletion is refused while active cargo references the zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone is soft-deleted and its locations are stripped from the openTCS plant model; the in-flight task breaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZoneService.remove() has no guard. Fix together with BR-12.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE-02: drop map topology editing; add UC 37/38/39; UC 32 narrowed to name and colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRS 1.3.2, 2.2, 1.5, 5.1, 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point/path/block management removed; 3 implemented UCs documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Topology is edited in the openTCS Model Editor, not in WES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deactivating an AGV removes it from the kernel entirely instead of leaving it in place as a static obstacle. AgvsService.disconnect() sets the vehicle's integration level to TO_BE_IGNORED and then disables the communication adapter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Park an AGV on a point that lies on a route other vehicles use. 2. Deactivate that AGV from the AGV list screen. 3. Create a transport request whose shortest route passes through that point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The AGV is no longer dispatched, but the kernel still treats the point it occupies as blocked, so other vehicles route around it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The kernel ignores the vehicle completely; other vehicles are routed straight through the occupied point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wes/src/agvs/agvs.service.ts:206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">openTCS provides TO_BE_RESPECTED for exactly this case - not dispatched, but its position still respected by the router. The change is one REST call, not new functionality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The zones and cargo controllers are guarded by authentication only, not by role, so any authenticated user including an Operator can call every mutation on those modules - including delete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in as a user holding the operator role. 2. Send DELETE /zones/{id} using that user's token.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The request is rejected with 403 Forbidden, as it is on the AGV and dispatch-policy controllers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The request succeeds and the record is deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wes/src/zones/zone.controller.ts:16; wes/src/cargo/cargo.controller.ts:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both declare @UseGuards(JwtAuthGuard) only. For comparison agvs.controller.ts:21 and dispatch-policy.controller.ts:22 declare @UseGuards(JwtAuthGuard, RolesGuard) with @Roles('admin'). These are the only two controllers with no role check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The isIgnored flag on an AGV can never be changed. It is declared on the entity and read in three places, but no DTO, endpoint or service method ever writes it, so it stays false for the lifetime of the record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open an AGV detail screen. 2. Attempt to exclude the AGV from orchestration (WBS #10). 3. Read the is_ignored column for that AGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flag is set to true and the assignment engine stops offering work to that AGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No request path writes the flag; it stays false and the AGV keeps receiving work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wes/src/agvs/entities/agv.entity.ts:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read at agvs.service.ts:103, assignment-engine.service.ts:570 and parking-engine.service.ts:130; every other occurrence is a test fixture. WBS #10 'Ignore AGV' and #11 'Restore ignored AGV' cannot be delivered until a write path exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The k-robustness safety buffer is honoured on only one of the two planning paths. The windowed PIBT fallback enforces it; the LaCAM search does not, and a plan violating the requested buffer is still returned and executed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set kRobust to 1. 2. Run a scenario in which the LaCAM search, not the windowed fallback, produces the plan. 3. Read the kernel log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A plan violating the requested buffer is rejected and the solver falls back to one that satisfies it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The plan is returned and used; the violation is only reported as an error in the log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LacamSolver.java:399; PibtEngine.java:311,329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enforcement exists at PibtEngine.java:311 and 329. The verifier isKRobust is called from finish() at line 399, which logs but does not reject; the message at line 401 states the limitation. Default kRobust is 0, so the gap stays latent until a non-zero value is configured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The plant-model parser reads &lt;property&gt; children of &lt;vehicle&gt; only. Properties declared on point, path, location and block elements are silently discarded, so a map uploaded through WES reaches the kernel with those settings missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add a property such as tcs:parkingPositionPriority to a point in the map XML. 2. Upload the map through WES. 3. Read that point back from the kernel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The property is present on the point in the kernel's plant model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The property is absent and no warning is emitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wes/src/opentcs/map-loader/opentcs-xml.parser.ts:259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only VehicleDto declares a properties field (line 46); PointDto, PathDto, LocationDto and BlockDto do not. Same defect class as the vehicle-property loss recorded in Issue I-005, which remains open for this reason.</t>
   </si>
 </sst>
 </file>
@@ -3131,7 +3353,7 @@
       </c>
       <c r="G5" s="8">
         <f>COUNTIFS(Defects!N5:N200,"Open",Defects!C5:C200,"&lt;&gt;")+COUNTIFS(Defects!N5:N200,"Pending",Defects!C5:C200,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
@@ -3156,7 +3378,7 @@
       </c>
       <c r="C8" s="8">
         <f>COUNTIFS(Defects!N5:N200,"Open",Defects!C5:C200,"&lt;&gt;")+COUNTIFS(Defects!N5:N200,"Pending",Defects!C5:C200,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D8" s="6">
         <f>COUNTIFS('Q&amp;A'!K5:K200,"Open",'Q&amp;A'!C5:C200,"&lt;&gt;")</f>
@@ -3202,8 +3424,9 @@
         <v>18</v>
       </c>
       <c r="E13" s="13"/>
-      <c r="F13" s="15" t="s">
-        <v>19</v>
+      <c r="F13" s="15" t="str">
+        <f>IF(COUNTA(Scope!B6:B6)=0,"",IF(COUNTIF(Scope!G6:G6,"Done")=COUNTA(Scope!B6:B6),"Done",IF(COUNTIF(Scope!G6:G6,"Not Started")=COUNTA(Scope!B6:B6),"Not Started","In Progress")))</f>
+        <v>Done</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -3217,8 +3440,9 @@
         <v>22</v>
       </c>
       <c r="E14" s="17"/>
-      <c r="F14" s="15" t="s">
-        <v>19</v>
+      <c r="F14" s="15" t="str">
+        <f>IF(COUNTA(Scope!B8:B10)=0,"",IF(COUNTIF(Scope!G8:G10,"Done")=COUNTA(Scope!B8:B10),"Done",IF(COUNTIF(Scope!G8:G10,"Not Started")=COUNTA(Scope!B8:B10),"Not Started","In Progress")))</f>
+        <v>Done</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -3232,8 +3456,9 @@
         <v>25</v>
       </c>
       <c r="E15" s="13"/>
-      <c r="F15" s="15" t="s">
-        <v>4</v>
+      <c r="F15" s="15" t="str">
+        <f>IF(COUNTA(Scope!B12:B15)=0,"",IF(COUNTIF(Scope!G12:G15,"Done")=COUNTA(Scope!B12:B15),"Done",IF(COUNTIF(Scope!G12:G15,"Not Started")=COUNTA(Scope!B12:B15),"Not Started","In Progress")))</f>
+        <v>Done</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -3247,7 +3472,10 @@
         <v>28</v>
       </c>
       <c r="E16" s="17"/>
-      <c r="F16" s="18"/>
+      <c r="F16" s="15" t="str">
+        <f>IF(COUNTA(Scope!B17:B36)=0,"",IF(COUNTIF(Scope!G17:G36,"Done")=COUNTA(Scope!B17:B36),"Done",IF(COUNTIF(Scope!G17:G36,"Not Started")=COUNTA(Scope!B17:B36),"Not Started","In Progress")))</f>
+        <v>Not Started</v>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="B17" s="12" t="s">
@@ -3260,7 +3488,10 @@
         <v>31</v>
       </c>
       <c r="E17" s="13"/>
-      <c r="F17" s="14"/>
+      <c r="F17" s="15" t="str">
+        <f>IF(COUNTA(Scope!B38:B41)=0,"",IF(COUNTIF(Scope!G38:G41,"Done")=COUNTA(Scope!B38:B41),"Done",IF(COUNTIF(Scope!G38:G41,"Not Started")=COUNTA(Scope!B38:B41),"Not Started","In Progress")))</f>
+        <v>Not Started</v>
+      </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="B18" s="16" t="s">
@@ -3273,7 +3504,10 @@
         <v>34</v>
       </c>
       <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="15" t="str">
+        <f>IF(COUNTA(Scope!B43:B44)=0,"",IF(COUNTIF(Scope!G43:G44,"Done")=COUNTA(Scope!B43:B44),"Done",IF(COUNTIF(Scope!G43:G44,"Not Started")=COUNTA(Scope!B43:B44),"Not Started","In Progress")))</f>
+        <v>Not Started</v>
+      </c>
     </row>
     <row r="19" ht="14.25" customHeight="1"/>
     <row r="20" ht="14.25" customHeight="1">
@@ -7543,7 +7777,7 @@
       </c>
       <c r="K23" s="60"/>
       <c r="L23" s="61" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M23" s="62"/>
       <c r="N23" s="36"/>
@@ -7696,7 +7930,7 @@
       </c>
       <c r="K26" s="60"/>
       <c r="L26" s="61" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M26" s="62"/>
       <c r="N26" s="36"/>
@@ -46123,25 +46357,25 @@
         <v>478</v>
       </c>
       <c r="B5" s="92" t="s">
-        <v>415</v>
+        <v>639</v>
       </c>
       <c r="C5" s="93" t="s">
-        <v>479</v>
+        <v>690</v>
       </c>
       <c r="D5" s="93" t="s">
-        <v>480</v>
+        <v>691</v>
       </c>
       <c r="E5" s="93" t="s">
-        <v>481</v>
+        <v>692</v>
       </c>
       <c r="F5" s="93" t="s">
-        <v>482</v>
+        <v>693</v>
       </c>
       <c r="G5" s="92" t="s">
-        <v>185</v>
+        <v>559</v>
       </c>
       <c r="H5" s="86" t="s">
-        <v>185</v>
+        <v>559</v>
       </c>
       <c r="I5" s="92" t="s">
         <v>483</v>
@@ -46154,157 +46388,259 @@
         <v>381</v>
       </c>
       <c r="M5" s="94" t="s">
-        <v>484</v>
+        <v>150</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="O5" s="92"/>
       <c r="P5" s="92"/>
       <c r="Q5" s="92" t="s">
         <v>422</v>
       </c>
-      <c r="R5" s="94"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
+      <c r="R5" s="94" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="6" ht="120.0" customHeight="1">
       <c r="A6" s="91" t="s">
         <v>486</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18" t="s">
+        <v>639</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>699</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>700</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>701</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>702</v>
+      </c>
       <c r="G6" s="86" t="s">
-        <v>185</v>
+        <v>559</v>
       </c>
       <c r="H6" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+        <v>559</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>578</v>
+      </c>
       <c r="M6" s="17"/>
       <c r="N6" s="32" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
       <c r="Q6" s="18"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
+      <c r="R6" s="17" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="7" ht="150.0" customHeight="1">
       <c r="A7" s="91" t="s">
         <v>487</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
+      <c r="B7" s="92" t="s">
+        <v>639</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>705</v>
+      </c>
+      <c r="D7" s="94" t="s">
+        <v>706</v>
+      </c>
+      <c r="E7" s="94" t="s">
+        <v>707</v>
+      </c>
+      <c r="F7" s="94" t="s">
+        <v>708</v>
+      </c>
       <c r="G7" s="86" t="s">
-        <v>185</v>
+        <v>657</v>
       </c>
       <c r="H7" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
+        <v>559</v>
+      </c>
+      <c r="I7" s="92" t="s">
+        <v>483</v>
+      </c>
+      <c r="J7" s="94" t="s">
+        <v>420</v>
+      </c>
+      <c r="K7" s="94" t="s">
+        <v>709</v>
+      </c>
+      <c r="L7" s="94" t="s">
+        <v>578</v>
+      </c>
       <c r="M7" s="94"/>
       <c r="N7" s="32" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="O7" s="92"/>
       <c r="P7" s="92"/>
       <c r="Q7" s="92"/>
-      <c r="R7" s="94"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
+      <c r="R7" s="94" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="8" ht="150.0" customHeight="1">
       <c r="A8" s="91" t="s">
         <v>488</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18" t="s">
+        <v>639</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>711</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>714</v>
+      </c>
       <c r="G8" s="86" t="s">
-        <v>185</v>
+        <v>559</v>
       </c>
       <c r="H8" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+        <v>559</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>578</v>
+      </c>
       <c r="M8" s="17"/>
       <c r="N8" s="32" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
       <c r="Q8" s="18"/>
-      <c r="R8" s="17"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
+      <c r="R8" s="17" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="9" ht="165.0" customHeight="1">
       <c r="A9" s="91" t="s">
         <v>489</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
+      <c r="B9" s="92" t="s">
+        <v>639</v>
+      </c>
+      <c r="C9" s="94" t="s">
+        <v>717</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>718</v>
+      </c>
+      <c r="E9" s="94" t="s">
+        <v>719</v>
+      </c>
+      <c r="F9" s="94" t="s">
+        <v>720</v>
+      </c>
       <c r="G9" s="86" t="s">
         <v>185</v>
       </c>
       <c r="H9" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="I9" s="92"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
+      <c r="I9" s="92" t="s">
+        <v>483</v>
+      </c>
+      <c r="J9" s="94" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="94" t="s">
+        <v>721</v>
+      </c>
+      <c r="L9" s="94" t="s">
+        <v>578</v>
+      </c>
       <c r="M9" s="94"/>
       <c r="N9" s="32" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="O9" s="92"/>
       <c r="P9" s="92"/>
       <c r="Q9" s="92"/>
-      <c r="R9" s="94"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
+      <c r="R9" s="94" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="10" ht="135.0" customHeight="1">
       <c r="A10" s="91" t="s">
         <v>490</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18" t="s">
+        <v>639</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>725</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>726</v>
+      </c>
       <c r="G10" s="86" t="s">
         <v>185</v>
       </c>
       <c r="H10" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="I10" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>727</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>578</v>
+      </c>
       <c r="M10" s="17"/>
       <c r="N10" s="32" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
-      <c r="R10" s="17"/>
+      <c r="R10" s="17" t="s">
+        <v>728</v>
+      </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="91" t="s">
@@ -49479,166 +49815,276 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1">
+    <row r="5" ht="195.0" customHeight="1">
       <c r="A5" s="96" t="s">
         <v>523</v>
       </c>
       <c r="B5" s="97" t="s">
-        <v>415</v>
+        <v>655</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>524</v>
+        <v>656</v>
       </c>
       <c r="D5" s="97" t="s">
         <v>525</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>185</v>
+        <v>657</v>
       </c>
       <c r="F5" s="99" t="s">
-        <v>526</v>
+        <v>658</v>
       </c>
       <c r="G5" s="99" t="s">
-        <v>381</v>
+        <v>578</v>
       </c>
       <c r="H5" s="99" t="s">
-        <v>527</v>
+        <v>578</v>
       </c>
       <c r="I5" s="97"/>
       <c r="J5" s="99" t="s">
-        <v>528</v>
+        <v>659</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L5" s="97"/>
-      <c r="M5" s="99"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
+        <v>660</v>
+      </c>
+      <c r="L5" s="97" t="s">
+        <v>661</v>
+      </c>
+      <c r="M5" s="99" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="6" ht="120.0" customHeight="1">
       <c r="A6" s="96" t="s">
         <v>529</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
+      <c r="B6" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>525</v>
+      </c>
       <c r="E6" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
+        <v>559</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>578</v>
+      </c>
       <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
+      <c r="J6" s="17" t="s">
+        <v>665</v>
+      </c>
       <c r="K6" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="17"/>
-    </row>
-    <row r="7" ht="19.5" customHeight="1">
+        <v>660</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="7" ht="165.0" customHeight="1">
       <c r="A7" s="96" t="s">
         <v>530</v>
       </c>
-      <c r="B7" s="97"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="97"/>
+      <c r="B7" s="97" t="s">
+        <v>667</v>
+      </c>
+      <c r="C7" s="99" t="s">
+        <v>668</v>
+      </c>
+      <c r="D7" s="97" t="s">
+        <v>525</v>
+      </c>
       <c r="E7" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
+        <v>657</v>
+      </c>
+      <c r="F7" s="99" t="s">
+        <v>669</v>
+      </c>
+      <c r="G7" s="99" t="s">
+        <v>578</v>
+      </c>
+      <c r="H7" s="99" t="s">
+        <v>578</v>
+      </c>
       <c r="I7" s="97"/>
-      <c r="J7" s="99"/>
+      <c r="J7" s="99" t="s">
+        <v>670</v>
+      </c>
       <c r="K7" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L7" s="97"/>
-      <c r="M7" s="99"/>
-    </row>
-    <row r="8" ht="19.5" customHeight="1">
+        <v>660</v>
+      </c>
+      <c r="L7" s="97" t="s">
+        <v>667</v>
+      </c>
+      <c r="M7" s="99" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="8" ht="105.0" customHeight="1">
       <c r="A8" s="96" t="s">
         <v>531</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>525</v>
+      </c>
       <c r="E8" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+        <v>559</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>673</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>578</v>
+      </c>
       <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
+      <c r="J8" s="17" t="s">
+        <v>674</v>
+      </c>
       <c r="K8" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="17"/>
-    </row>
-    <row r="9" ht="19.5" customHeight="1">
+        <v>660</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" ht="150.0" customHeight="1">
       <c r="A9" s="96" t="s">
         <v>532</v>
       </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="97"/>
+      <c r="B9" s="97" t="s">
+        <v>676</v>
+      </c>
+      <c r="C9" s="99" t="s">
+        <v>677</v>
+      </c>
+      <c r="D9" s="97" t="s">
+        <v>525</v>
+      </c>
       <c r="E9" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
+        <v>657</v>
+      </c>
+      <c r="F9" s="99" t="s">
+        <v>678</v>
+      </c>
+      <c r="G9" s="99" t="s">
+        <v>578</v>
+      </c>
+      <c r="H9" s="99" t="s">
+        <v>578</v>
+      </c>
       <c r="I9" s="97"/>
-      <c r="J9" s="99"/>
+      <c r="J9" s="99" t="s">
+        <v>679</v>
+      </c>
       <c r="K9" s="32" t="s">
         <v>385</v>
       </c>
       <c r="L9" s="97"/>
-      <c r="M9" s="99"/>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
+      <c r="M9" s="99" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="10" ht="180.0" customHeight="1">
       <c r="A10" s="96" t="s">
         <v>533</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="18" t="s">
+        <v>681</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>525</v>
+      </c>
       <c r="E10" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
+        <v>559</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>683</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>578</v>
+      </c>
       <c r="I10" s="18"/>
-      <c r="J10" s="17"/>
+      <c r="J10" s="17" t="s">
+        <v>684</v>
+      </c>
       <c r="K10" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="17"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
+        <v>660</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>639</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="11" ht="225.0" customHeight="1">
       <c r="A11" s="96" t="s">
         <v>534</v>
       </c>
-      <c r="B11" s="97"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="97"/>
+      <c r="B11" s="97" t="s">
+        <v>661</v>
+      </c>
+      <c r="C11" s="99" t="s">
+        <v>686</v>
+      </c>
+      <c r="D11" s="97" t="s">
+        <v>525</v>
+      </c>
       <c r="E11" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
+        <v>566</v>
+      </c>
+      <c r="F11" s="99" t="s">
+        <v>687</v>
+      </c>
+      <c r="G11" s="99" t="s">
+        <v>578</v>
+      </c>
+      <c r="H11" s="99" t="s">
+        <v>578</v>
+      </c>
       <c r="I11" s="97"/>
-      <c r="J11" s="99"/>
+      <c r="J11" s="99" t="s">
+        <v>688</v>
+      </c>
       <c r="K11" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L11" s="97"/>
-      <c r="M11" s="99"/>
+        <v>660</v>
+      </c>
+      <c r="L11" s="97" t="s">
+        <v>661</v>
+      </c>
+      <c r="M11" s="99" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="96" t="s">
@@ -53831,13 +54277,27 @@
       <c r="A8" s="105" t="s">
         <v>616</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>639</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>695</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>649</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>648</v>
+      </c>
       <c r="I8" s="86" t="s">
         <v>185</v>
       </c>
@@ -53845,7 +54305,9 @@
       <c r="K8" s="32" t="s">
         <v>485</v>
       </c>
-      <c r="L8" s="17"/>
+      <c r="L8" s="17" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="105" t="s">
